--- a/stories/arbres/TREE-REL-008.xlsx
+++ b/stories/arbres/TREE-REL-008.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sur le chemin de l'école, Zoé voit un enfant tout seul, près du muret. Les autres marchent plus loin. Papa tient la main de Zoé. Maman a mis le cartable. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Près du train, un enfant reste à l'écart. C'est le train. La fenêtre tremble un tout petit peu. Zoé s'approche, sans courir. Maman n'est pas loin. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1857,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Un enfant est à l'écart. Que fait-on ? Avec le train.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2030,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé retient le geste. Elle respire.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2181,6 +2223,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2345,6 +2392,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi Tom, après le train. Un nuage passe devant le soleil. Zoé montre Tom à papa. Elle nomme ce qu'elle sent. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2583,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2750,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le matin, après le train et Tom. La tasse est encore tiède. On dit merci. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé quitte ce moment et va vers papa. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2917,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3084,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint après la sieste, après le train et Tom. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé nomme encore le mot, tout bas. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3251,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3418,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le soir, après le train et Tom. Une abeille bourdonne loin. On attend un petit moment. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé boit une gorgée. Elle se sent plus légère. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3585,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3752,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi Léa, après le train. Ça sent le savon de maman. On continue avec Léa. Zoé gardu geste sûr. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3943,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4110,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le matin, après le train et Léa. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé serre la main de papa, tout doux. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4277,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4444,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint après la sieste, après le train et Léa. La fenêtre tremble un tout petit peu. On sourit un peu. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé quitte ce moment et va vers papa. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4611,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4778,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le soir, après le train et Léa. Ça sent le savon de maman. On boit une gorgée d'eau. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé dit merci à papa. Maman sourit. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4945,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5112,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi Sami, après le train. Le lait est tiède. Zoé attend près de Sami. Elle ne prend pas de force. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5303,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5470,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le matin, après le train et Sami. Un pigeon roucoule. On essuie une miette. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé nomme encore le mot, tout bas. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5637,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5804,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint après la sieste, après le train et Sami. La cuillère tinte. On referme un livre. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé serre la main de papa, tout doux. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5971,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6138,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le soir, après le train et Sami. Le ballon est un peu poudreux. On pose un jouet à sa place. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé range le soir un instant. Puis elle reprend, calme. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6305,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6305,6 +6472,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Près du bus, un enfant reste à l'écart. Zoé s'occupe du bus. La corbeille craque. Papa sourit. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6481,6 +6653,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Un enfant est à l'écart. Que fait-on ? Avec le bus.</t>
         </is>
       </c>
     </row>
@@ -6649,6 +6826,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé répète le mot. Papa hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6837,6 +7019,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7001,6 +7188,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi Tom, après le bus. Le train souffle au loin. Zoé s'installe avec Tom. Papa reste à portée de voix. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7379,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7546,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le matin, après le bus et Tom. Une goutte de pluie sèche déjà. On marche tout doucement. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé nomme encore le mot, tout bas. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7713,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7880,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint après la sieste, après le bus et Tom. Le banc est tiède. On se tait une seconde. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé nomme encore le mot, tout bas. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8047,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8214,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le soir, après le bus et Tom. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé dit merci à papa. Maman sourit. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8381,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8548,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi Léa, après le bus. Le pain croustille. Zoé attend près de Léa. Elle ne prend pas de force. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8739,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8906,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le matin, après le bus et Léa. Une feuille tourne et tombe. On s'assoit près de l'adulte. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé dit merci à papa. Maman sourit. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9073,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9240,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint après la sieste, après le bus et Léa. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé dit merci à papa. Maman sourit. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9407,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9574,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le soir, après le bus et Léa. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. On laisse le soir à sa place. Zoé est près de papa. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9741,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9908,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi Sami, après le bus. Le coussin est moelleux. Zoé choisit Sami. Maman n'est pas loin. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10099,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9989,6 +10266,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le matin, après le bus et Sami. Une plume vole. On range les chaussures. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. On laisse le matin à sa place. Zoé est près de papa. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10433,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10600,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint après la sieste, après le bus et Sami. Le pain croustille. On met le doudou près de soi. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. On laisse après la sieste à sa place. Zoé est près de papa. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10767,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10934,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le soir, après le bus et Sami. La laine du doudou est douce. On écoute le cœur, tout doux. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. On laisse le soir à sa place. Zoé est près de papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11101,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10961,6 +11268,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Près de la voiture, un enfant reste à l'écart. Voilà la voiture. La fenêtre tremble un tout petit peu. Zoé pose les pieds par terre, près de papa. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11137,6 +11449,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Un enfant est à l'écart. Que fait-on ? Avec la voiture.</t>
         </is>
       </c>
     </row>
@@ -11305,6 +11622,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé pose les pieds par terre. On continue, tout calme.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11493,6 +11815,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -11657,6 +11984,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi Tom, après la voiture. La tasse est encore tiède. Zoé choisit Tom. Maman n'est pas loin. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12175,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12342,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le matin, après la voiture et Tom. Un galet est lisse dans la main. On secoue les mains, loin. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé quitte ce moment et va vers papa. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12509,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12676,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint après la sieste, après la voiture et Tom. Le train souffle au loin. On pose le sac. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé quitte ce moment et va vers papa. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12843,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13010,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le soir, après la voiture et Tom. Une vache meugle, loin. On dit le mot de l'émotion. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé range le soir un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13177,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13344,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi Léa, après la voiture. Le coussin est moelleux. Léa est là. Zoé pose les mains à vue, loin de l'autre. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13535,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13187,7 +13564,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le matin, après la voiture et Léa. Un grillon chante, tout petit. On invite d'une petite voix. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Papa dit : je t'ai entendu. Maman aussi. On gardu geste.</t>
+          <t>Zoé rejoint le matin, après la voiture et Léa. Un grillon chante, tout petit. On invite d'une petite voix. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Je t'ai entendu. Maman aussi. On gardu geste.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13325,6 +13702,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le matin, après la voiture et Léa. Un grillon chante, tout petit. On invite d'une petite voix. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.
+papa|Je t'ai entendu. Maman aussi. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13870,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13511,7 +13899,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint après la sieste, après la voiture et Léa. Le bois de la table est lisse. On attend la réponse. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Papa dit : je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
+          <t>Zoé rejoint après la sieste, après la voiture et Léa. Le bois de la table est lisse. On attend la réponse. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -13649,6 +14037,12 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint après la sieste, après la voiture et Léa. Le bois de la table est lisse. On attend la réponse. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.
+papa|Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14205,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14372,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le soir, après la voiture et Léa. Une goutte tombe dans l'évier. On propose une autre idée. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé quitte ce moment et va vers papa. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14539,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14159,7 +14568,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi Sami, après la voiture. Un nuage passe devant le soleil. Zoé touche Sami tout doucement. Papa dit : je suis là. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
+          <t>Zoé a choisi Sami, après la voiture. Un nuage passe devant le soleil. Zoé touche Sami tout doucement. Je suis là. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14297,6 +14706,13 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi Sami, après la voiture. Un nuage passe devant le soleil. Zoé touche Sami tout doucement.
+papa|Je suis là.
+narrateur|Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14899,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15066,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le matin, après la voiture et Sami. Le toboggan est un peu froid. On va vers papa ou maman. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé boit une gorgée. Elle se sent plus légère. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15233,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15400,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint après la sieste, après la voiture et Sami. La clochette de la porte tinte. On dit stop, tout clair. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé boit une gorgée. Elle se sent plus légère. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15567,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15155,7 +15596,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le soir, après la voiture et Sami. Ça sent le thym du jardin. On s'éloigne d'un pas. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Papa dit : je t'ai entendu. Maman aussi. On se serre un peu.</t>
+          <t>Zoé rejoint le soir, après la voiture et Sami. Ça sent le thym du jardin. On s'éloigne d'un pas. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Je t'ai entendu. Maman aussi. On se serre un peu.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15293,6 +15734,12 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le soir, après la voiture et Sami. Ça sent le thym du jardin. On s'éloigne d'un pas. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.
+papa|Je t'ai entendu. Maman aussi. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15902,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15504,6 +15956,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-REL-008.xlsx
+++ b/stories/arbres/TREE-REL-008.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Sur le chemin de l'école, Zoé voit un enfant tout seul, près du muret. Les autres marchent plus loin. Papa tient la main de Zoé. Maman a mis le cartable. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1688,7 @@
           <t>narrateur|Près du train, un enfant reste à l'écart. C'est le train. La fenêtre tremble un tout petit peu. Zoé s'approche, sans courir. Maman n'est pas loin. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1864,6 +1872,7 @@
           <t>narrateur|Un enfant est à l'écart. Que fait-on ? Avec le train.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2035,6 +2044,7 @@
           <t>narrateur|Oui. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé retient le geste. Elle respire.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2230,6 +2240,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2397,6 +2408,7 @@
           <t>narrateur|Zoé a choisi Tom, après le train. Un nuage passe devant le soleil. Zoé montre Tom à papa. Elle nomme ce qu'elle sent. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2588,6 +2600,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2755,6 +2768,7 @@
           <t>narrateur|Zoé rejoint le matin, après le train et Tom. La tasse est encore tiède. On dit merci. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé quitte ce moment et va vers papa. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2922,6 +2936,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3089,6 +3104,7 @@
           <t>narrateur|Zoé rejoint après la sieste, après le train et Tom. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé nomme encore le mot, tout bas. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3256,6 +3272,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3423,6 +3440,7 @@
           <t>narrateur|Zoé rejoint le soir, après le train et Tom. Une abeille bourdonne loin. On attend un petit moment. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé boit une gorgée. Elle se sent plus légère. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3590,6 +3608,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3757,6 +3776,7 @@
           <t>narrateur|Zoé a choisi Léa, après le train. Ça sent le savon de maman. On continue avec Léa. Zoé gardu geste sûr. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3948,6 +3968,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4115,6 +4136,7 @@
           <t>narrateur|Zoé rejoint le matin, après le train et Léa. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé serre la main de papa, tout doux. On respire.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4282,6 +4304,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4449,6 +4472,7 @@
           <t>narrateur|Zoé rejoint après la sieste, après le train et Léa. La fenêtre tremble un tout petit peu. On sourit un peu. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé quitte ce moment et va vers papa. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4616,6 +4640,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4783,6 +4808,7 @@
           <t>narrateur|Zoé rejoint le soir, après le train et Léa. Ça sent le savon de maman. On boit une gorgée d'eau. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé dit merci à papa. Maman sourit. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4950,6 +4976,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5117,6 +5144,7 @@
           <t>narrateur|Zoé a choisi Sami, après le train. Le lait est tiède. Zoé attend près de Sami. Elle ne prend pas de force. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5308,6 +5336,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5475,6 +5504,7 @@
           <t>narrateur|Zoé rejoint le matin, après le train et Sami. Un pigeon roucoule. On essuie une miette. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé nomme encore le mot, tout bas. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5642,6 +5672,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5809,6 +5840,7 @@
           <t>narrateur|Zoé rejoint après la sieste, après le train et Sami. La cuillère tinte. On referme un livre. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé serre la main de papa, tout doux. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5976,6 +6008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6143,6 +6176,7 @@
           <t>narrateur|Zoé rejoint le soir, après le train et Sami. Le ballon est un peu poudreux. On pose un jouet à sa place. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé range le soir un instant. Puis elle reprend, calme. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6310,6 +6344,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6477,6 +6512,7 @@
           <t>narrateur|Près du bus, un enfant reste à l'écart. Zoé s'occupe du bus. La corbeille craque. Papa sourit. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6660,6 +6696,7 @@
           <t>narrateur|Un enfant est à l'écart. Que fait-on ? Avec le bus.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6831,6 +6868,7 @@
           <t>narrateur|Oui. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé répète le mot. Papa hoche la tête.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7026,6 +7064,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7193,6 +7232,7 @@
           <t>narrateur|Zoé a choisi Tom, après le bus. Le train souffle au loin. Zoé s'installe avec Tom. Papa reste à portée de voix. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7384,6 +7424,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7551,6 +7592,7 @@
           <t>narrateur|Zoé rejoint le matin, après le bus et Tom. Une goutte de pluie sèche déjà. On marche tout doucement. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé nomme encore le mot, tout bas. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7718,6 +7760,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7885,6 +7928,7 @@
           <t>narrateur|Zoé rejoint après la sieste, après le bus et Tom. Le banc est tiède. On se tait une seconde. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé nomme encore le mot, tout bas. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8052,6 +8096,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8219,6 +8264,7 @@
           <t>narrateur|Zoé rejoint le soir, après le bus et Tom. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé dit merci à papa. Maman sourit. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8386,6 +8432,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8553,6 +8600,7 @@
           <t>narrateur|Zoé a choisi Léa, après le bus. Le pain croustille. Zoé attend près de Léa. Elle ne prend pas de force. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8744,6 +8792,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8911,6 +8960,7 @@
           <t>narrateur|Zoé rejoint le matin, après le bus et Léa. Une feuille tourne et tombe. On s'assoit près de l'adulte. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé dit merci à papa. Maman sourit. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9078,6 +9128,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9245,6 +9296,7 @@
           <t>narrateur|Zoé rejoint après la sieste, après le bus et Léa. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé dit merci à papa. Maman sourit. On respire.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9412,6 +9464,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9579,6 +9632,7 @@
           <t>narrateur|Zoé rejoint le soir, après le bus et Léa. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. On laisse le soir à sa place. Zoé est près de papa. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9746,6 +9800,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9913,6 +9968,7 @@
           <t>narrateur|Zoé a choisi Sami, après le bus. Le coussin est moelleux. Zoé choisit Sami. Maman n'est pas loin. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10104,6 +10160,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10271,6 +10328,7 @@
           <t>narrateur|Zoé rejoint le matin, après le bus et Sami. Une plume vole. On range les chaussures. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. On laisse le matin à sa place. Zoé est près de papa. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10438,6 +10496,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10605,6 +10664,7 @@
           <t>narrateur|Zoé rejoint après la sieste, après le bus et Sami. Le pain croustille. On met le doudou près de soi. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. On laisse après la sieste à sa place. Zoé est près de papa. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10772,6 +10832,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10939,6 +11000,7 @@
           <t>narrateur|Zoé rejoint le soir, après le bus et Sami. La laine du doudou est douce. On écoute le cœur, tout doux. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. On laisse le soir à sa place. Zoé est près de papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11106,6 +11168,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11273,6 +11336,7 @@
           <t>narrateur|Près de la voiture, un enfant reste à l'écart. Voilà la voiture. La fenêtre tremble un tout petit peu. Zoé pose les pieds par terre, près de papa. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11456,6 +11520,7 @@
           <t>narrateur|Un enfant est à l'écart. Que fait-on ? Avec la voiture.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11627,6 +11692,7 @@
           <t>narrateur|Oui. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11822,6 +11888,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11989,6 +12056,7 @@
           <t>narrateur|Zoé a choisi Tom, après la voiture. La tasse est encore tiède. Zoé choisit Tom. Maman n'est pas loin. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12180,6 +12248,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12347,6 +12416,7 @@
           <t>narrateur|Zoé rejoint le matin, après la voiture et Tom. Un galet est lisse dans la main. On secoue les mains, loin. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé quitte ce moment et va vers papa. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12514,6 +12584,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12681,6 +12752,7 @@
           <t>narrateur|Zoé rejoint après la sieste, après la voiture et Tom. Le train souffle au loin. On pose le sac. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé quitte ce moment et va vers papa. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12848,6 +12920,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13015,6 +13088,7 @@
           <t>narrateur|Zoé rejoint le soir, après la voiture et Tom. Une vache meugle, loin. On dit le mot de l'émotion. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé range le soir un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13182,6 +13256,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13349,6 +13424,7 @@
           <t>narrateur|Zoé a choisi Léa, après la voiture. Le coussin est moelleux. Léa est là. Zoé pose les mains à vue, loin de l'autre. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13540,6 +13616,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13708,6 +13785,7 @@
 papa|Je t'ai entendu. Maman aussi. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13875,6 +13953,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14043,6 +14122,7 @@
 papa|Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14210,6 +14290,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14377,6 +14458,7 @@
           <t>narrateur|Zoé rejoint le soir, après la voiture et Léa. Une goutte tombe dans l'évier. On propose une autre idée. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé quitte ce moment et va vers papa. On respire.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14544,6 +14626,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14713,6 +14796,7 @@
 narrateur|Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14904,6 +14988,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15071,6 +15156,7 @@
           <t>narrateur|Zoé rejoint le matin, après la voiture et Sami. Le toboggan est un peu froid. On va vers papa ou maman. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé boit une gorgée. Elle se sent plus légère. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15238,6 +15324,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15405,6 +15492,7 @@
           <t>narrateur|Zoé rejoint après la sieste, après la voiture et Sami. La clochette de la porte tinte. On dit stop, tout clair. Zoé va rejoindre celui qui est à l'écart. Elle l'invite. Si ça continue, Zoé prévient un adulte, papa. Zoé boit une gorgée. Elle se sent plus légère. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15572,6 +15660,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15740,6 +15829,7 @@
 papa|Je t'ai entendu. Maman aussi. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15907,6 +15997,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15925,7 +16016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15963,6 +16054,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15977,7 +16082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16164,6 +16269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
